--- a/db/OLEO26.xlsx
+++ b/db/OLEO26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D9E0E2-4AE6-43BD-BA08-477831434E56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E991608-C53C-4F18-B6C4-A36D3A57C22F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2358,8 +2358,15 @@
     <col min="8" max="8" width="11.44140625" style="3" customWidth="1"/>
     <col min="9" max="9" width="11.44140625" style="2" customWidth="1"/>
     <col min="10" max="10" width="50" style="1" customWidth="1"/>
-    <col min="11" max="16" width="11.44140625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="31.21875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.77734375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="53.21875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="28" style="1" customWidth="1"/>
+    <col min="16" max="16" width="67.109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="19.21875" customWidth="1"/>
+    <col min="18" max="18" width="19.33203125" customWidth="1"/>
+    <col min="21" max="21" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">

--- a/db/OLEO26.xlsx
+++ b/db/OLEO26.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E991608-C53C-4F18-B6C4-A36D3A57C22F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940"/>
   </bookViews>
   <sheets>
-    <sheet name="OLEO26" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="OLEO26" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Database">OLEO26!$A$1:$U$158</definedName>
@@ -18,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="655">
   <si>
     <t>DATA</t>
   </si>
@@ -83,7 +82,7 @@
     <t>LIQUIDADO</t>
   </si>
   <si>
-    <t>CODIGO</t>
+    <t>29/10/2026</t>
   </si>
   <si>
     <t>O.8</t>
@@ -111,6 +110,9 @@
   </si>
   <si>
     <t>** QUANTIDADE ORIGINAL DO CONTRATO:  175 TONS **</t>
+  </si>
+  <si>
+    <t>teste 1</t>
   </si>
   <si>
     <t>002</t>
@@ -1985,25 +1987,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2026,12 +2028,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2349,9 +2352,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V166"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:X166"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="11.44140625" customHeight="1"/>
   <cols>
     <col min="2" max="6" width="11.44140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.44140625" style="2" customWidth="1"/>
@@ -2369,7 +2372,7 @@
     <col min="21" max="21" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2433,13 +2436,10 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>46027</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>22</v>
@@ -2493,27 +2493,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>46027</v>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G3" s="2">
-        <v>75.260000000000005</v>
+        <v>75.26</v>
       </c>
       <c r="H3" s="3">
         <v>6780</v>
@@ -2522,17 +2522,20 @@
         <v>1</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="M3" s="1"/>
       <c r="N3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>35</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="P3" s="1"/>
       <c r="Q3" s="4">
         <v>46027</v>
       </c>
@@ -2549,24 +2552,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46028</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" s="2">
         <v>1200</v>
@@ -2578,10 +2581,10 @@
         <v>0.5</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q4" s="4">
         <v>46054</v>
@@ -2599,24 +2602,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>46028</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2">
         <v>2000</v>
@@ -2628,19 +2631,19 @@
         <v>0.5</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="4">
         <v>46054</v>
@@ -2658,24 +2661,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46029</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="2">
         <v>1500</v>
@@ -2687,10 +2690,10 @@
         <v>0.5</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q6" s="4">
         <v>46054</v>
@@ -2708,7 +2711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>46029</v>
       </c>
@@ -2716,19 +2719,19 @@
         <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7" s="2">
-        <v>499.12099999999998</v>
+        <v>499.121</v>
       </c>
       <c r="H7" s="3">
         <v>5650</v>
@@ -2737,16 +2740,16 @@
         <v>0.5</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q7" s="4">
         <v>46030</v>
@@ -2764,27 +2767,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>46029</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8" s="2">
-        <v>527.67999999999995</v>
+        <v>527.68</v>
       </c>
       <c r="H8" s="3">
         <v>5500</v>
@@ -2793,22 +2796,22 @@
         <v>0.5</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q8" s="4">
         <v>46030</v>
@@ -2826,27 +2829,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>46029</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2">
-        <v>983.28099999999995</v>
+        <v>983.281</v>
       </c>
       <c r="H9" s="3">
         <v>5700</v>
@@ -2855,16 +2858,16 @@
         <v>0.5</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q9" s="4">
         <v>46047</v>
@@ -2881,25 +2884,26 @@
       <c r="U9" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X9" s="5"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46029</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" s="2">
         <v>1004.72</v>
@@ -2911,19 +2915,19 @@
         <v>0.5</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q10" s="4">
         <v>46043</v>
@@ -2941,21 +2945,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>46030</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>26</v>
@@ -2970,16 +2974,16 @@
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q11" s="4">
         <v>46034</v>
@@ -2997,27 +3001,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46031</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G12" s="2">
-        <v>1051.3499999999999</v>
+        <v>1051.35</v>
       </c>
       <c r="H12" s="3">
         <v>5850</v>
@@ -3026,13 +3030,13 @@
         <v>0.5</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q12" s="4">
         <v>46038</v>
@@ -3050,24 +3054,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>46036</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G13" s="2">
         <v>999.91</v>
@@ -3079,13 +3083,13 @@
         <v>0.5</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q13" s="4">
         <v>46054</v>
@@ -3103,27 +3107,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46036</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G14" s="2">
-        <v>998.94799999999998</v>
+        <v>998.948</v>
       </c>
       <c r="H14" s="3">
         <v>6300</v>
@@ -3132,13 +3136,13 @@
         <v>0.5</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q14" s="4">
         <v>46082</v>
@@ -3156,24 +3160,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>46037</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G15" s="2">
         <v>228.07</v>
@@ -3185,13 +3189,13 @@
         <v>0.5</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="4">
         <v>46037</v>
@@ -3209,24 +3213,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46038</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G16" s="2">
         <v>1000</v>
@@ -3238,13 +3242,13 @@
         <v>0.25</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q16" s="4">
         <v>46038</v>
@@ -3267,19 +3271,19 @@
         <v>46044</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G17" s="2">
         <v>1000</v>
@@ -3288,19 +3292,19 @@
         <v>6260.94</v>
       </c>
       <c r="I17" s="2">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q17" s="4">
         <v>46082</v>
@@ -3323,19 +3327,19 @@
         <v>46045</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G18" s="2">
         <v>300</v>
@@ -3347,13 +3351,13 @@
         <v>0.5</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q18" s="4">
         <v>46054</v>
@@ -3371,24 +3375,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>46048</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G19" s="2">
         <v>2000</v>
@@ -3400,16 +3404,16 @@
         <v>0.3</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q19" s="4">
         <v>46048</v>
@@ -3432,16 +3436,16 @@
         <v>46050</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>26</v>
@@ -3456,16 +3460,16 @@
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q20" s="4">
         <v>46054</v>
@@ -3488,19 +3492,19 @@
         <v>46057</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G21" s="2">
         <v>1000</v>
@@ -3509,19 +3513,19 @@
         <v>6306.24</v>
       </c>
       <c r="I21" s="2">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q21" s="4">
         <v>46082</v>
@@ -3544,19 +3548,19 @@
         <v>46056</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G22" s="2">
         <v>2000</v>
@@ -3565,19 +3569,19 @@
         <v>6306.24</v>
       </c>
       <c r="I22" s="2">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q22" s="4">
         <v>46082</v>
@@ -3600,19 +3604,19 @@
         <v>46056</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G23" s="2">
         <v>1000</v>
@@ -3621,19 +3625,19 @@
         <v>6306.24</v>
       </c>
       <c r="I23" s="2">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q23" s="4">
         <v>46082</v>
@@ -3656,19 +3660,19 @@
         <v>46058</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G24" s="2">
         <v>500.29</v>
@@ -3680,13 +3684,13 @@
         <v>0.5</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q24" s="4">
         <v>46059</v>
@@ -3709,19 +3713,19 @@
         <v>46058</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G25" s="2">
         <v>600</v>
@@ -3733,16 +3737,16 @@
         <v>0.5</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q25" s="4">
         <v>46082</v>
@@ -3768,13 +3772,13 @@
         <v>22</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>26</v>
@@ -3789,22 +3793,22 @@
         <v>1</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q26" s="4">
         <v>46063</v>
@@ -3827,16 +3831,16 @@
         <v>46059</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>26</v>
@@ -3851,16 +3855,16 @@
         <v>0.5</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>29</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q27" s="4">
         <v>46059</v>
@@ -3883,19 +3887,19 @@
         <v>46062</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G28" s="2">
         <v>504.6</v>
@@ -3907,13 +3911,13 @@
         <v>0.5</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q28" s="4">
         <v>46062</v>
@@ -3939,16 +3943,16 @@
         <v>22</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G29" s="2">
         <v>986.88</v>
@@ -3960,19 +3964,19 @@
         <v>0.5</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q29" s="4">
         <v>46066</v>
@@ -3990,21 +3994,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>46071</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>26</v>
@@ -4019,16 +4023,16 @@
         <v>1</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q30" s="4">
         <v>46071</v>
@@ -4046,24 +4050,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" ht="14.4" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>46072</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G31" s="2">
         <v>999.92</v>
@@ -4075,13 +4079,13 @@
         <v>0.5</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q31" s="4">
         <v>46055</v>
@@ -4099,24 +4103,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>46076</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G32" s="2">
         <v>2000</v>
@@ -4128,13 +4132,13 @@
         <v>0.3</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q32" s="4">
         <v>46078</v>
@@ -4152,24 +4156,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>46077</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G33" s="2">
         <v>500</v>
@@ -4181,13 +4185,13 @@
         <v>0.5</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q33" s="4">
         <v>46085</v>
@@ -4205,7 +4209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>46077</v>
       </c>
@@ -4213,13 +4217,13 @@
         <v>22</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>26</v>
@@ -4234,19 +4238,19 @@
         <v>1</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q34" s="4">
         <v>46077</v>
@@ -4264,24 +4268,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>46084</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G35" s="2">
         <v>1000</v>
@@ -4293,10 +4297,10 @@
         <v>0.5</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q35" s="4">
         <v>46113</v>
@@ -4314,24 +4318,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>46085</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G36" s="2">
         <v>500</v>
@@ -4343,16 +4347,16 @@
         <v>0.5</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q36" s="4">
         <v>46113</v>
@@ -4370,24 +4374,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>46085</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G37" s="2">
         <v>1032.46</v>
@@ -4399,22 +4403,22 @@
         <v>0.5</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q37" s="4">
         <v>46143</v>
@@ -4432,24 +4436,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>46085</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G38" s="2">
         <v>495.26</v>
@@ -4461,16 +4465,16 @@
         <v>0.5</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q38" s="4">
         <v>46143</v>
@@ -4488,24 +4492,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>46085</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G39" s="2">
         <v>1002.17</v>
@@ -4517,13 +4521,13 @@
         <v>0.5</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q39" s="4">
         <v>46113</v>
@@ -4541,24 +4545,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>46087</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G40" s="2">
         <v>1007.3</v>
@@ -4570,16 +4574,16 @@
         <v>0.5</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q40" s="4">
         <v>46090</v>
@@ -4597,7 +4601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>46091</v>
       </c>
@@ -4605,19 +4609,19 @@
         <v>22</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="2">
-        <v>34.700000000000003</v>
+        <v>34.7</v>
       </c>
       <c r="H41" s="3">
         <v>7050</v>
@@ -4626,13 +4630,13 @@
         <v>1</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q41" s="4">
         <v>46091</v>
@@ -4650,24 +4654,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>46094</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G42" s="2">
         <v>973.7</v>
@@ -4679,13 +4683,13 @@
         <v>0.5</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q42" s="4">
         <v>46113</v>
@@ -4703,24 +4707,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>46097</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G43" s="2">
         <v>1017.929</v>
@@ -4732,16 +4736,16 @@
         <v>0.5</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q43" s="4">
         <v>46098</v>
@@ -4759,24 +4763,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>46098</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G44" s="2">
         <v>400</v>
@@ -4788,10 +4792,10 @@
         <v>0.5</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q44" s="4">
         <v>46099</v>
@@ -4809,27 +4813,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>46100</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G45" s="2">
-        <v>279.10000000000002</v>
+        <v>279.1</v>
       </c>
       <c r="H45" s="3">
         <v>5650</v>
@@ -4838,16 +4842,16 @@
         <v>0.5</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q45" s="4">
         <v>46113</v>
@@ -4865,24 +4869,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>46105</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G46" s="2">
         <v>2000</v>
@@ -4894,10 +4898,10 @@
         <v>0.3</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q46" s="4">
         <v>46105</v>
@@ -4915,27 +4919,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>46107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G47" s="2">
-        <v>998.99300000000005</v>
+        <v>998.993</v>
       </c>
       <c r="H47" s="3">
         <v>6400</v>
@@ -4944,13 +4948,13 @@
         <v>0.5</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q47" s="4">
         <v>46111</v>
@@ -4968,24 +4972,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46108</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G48" s="2">
         <v>139.65</v>
@@ -4997,13 +5001,13 @@
         <v>0.5</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q48" s="4">
         <v>46134</v>
@@ -5021,24 +5025,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>46119</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G49" s="2">
         <v>985.82</v>
@@ -5050,13 +5054,13 @@
         <v>0.5</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q49" s="4">
         <v>46120</v>
@@ -5074,24 +5078,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>46120</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G50" s="2">
         <v>1000</v>
@@ -5103,10 +5107,10 @@
         <v>0.5</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q50" s="4">
         <v>46143</v>
@@ -5124,27 +5128,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>46121</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G51" s="2">
-        <v>980.58199999999999</v>
+        <v>980.582</v>
       </c>
       <c r="H51" s="3">
         <v>6500</v>
@@ -5153,22 +5157,22 @@
         <v>0.5</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q51" s="4">
         <v>46122</v>
@@ -5186,24 +5190,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>46122</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G52" s="2">
         <v>506.39</v>
@@ -5215,13 +5219,13 @@
         <v>0.25</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q52" s="4">
         <v>46122</v>
@@ -5239,24 +5243,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>46122</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G53" s="2">
         <v>1981.04</v>
@@ -5268,16 +5272,16 @@
         <v>0.5</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q53" s="4">
         <v>46174</v>
@@ -5295,7 +5299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>46125</v>
       </c>
@@ -5303,16 +5307,16 @@
         <v>22</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G54" s="2">
         <v>1011.04</v>
@@ -5324,13 +5328,13 @@
         <v>0.5</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q54" s="4">
         <v>46143</v>
@@ -5348,7 +5352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>46125</v>
       </c>
@@ -5356,19 +5360,19 @@
         <v>22</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G55" s="2">
-        <v>993.07899999999995</v>
+        <v>993.079</v>
       </c>
       <c r="H55" s="3">
         <v>5760</v>
@@ -5377,22 +5381,22 @@
         <v>0.5</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q55" s="4">
         <v>46126</v>
@@ -5410,24 +5414,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>46126</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G56" s="2">
         <v>1000</v>
@@ -5439,10 +5443,10 @@
         <v>0.5</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q56" s="4">
         <v>46143</v>
@@ -5460,24 +5464,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>46126</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G57" s="2">
         <v>1000</v>
@@ -5489,10 +5493,10 @@
         <v>0.5</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q57" s="4">
         <v>46174</v>
@@ -5510,7 +5514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>46127</v>
       </c>
@@ -5518,7 +5522,7 @@
         <v>22</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>24</v>
@@ -5530,7 +5534,7 @@
         <v>26</v>
       </c>
       <c r="G58" s="2">
-        <v>155.80000000000001</v>
+        <v>155.8</v>
       </c>
       <c r="H58" s="3">
         <v>7850</v>
@@ -5539,16 +5543,16 @@
         <v>1</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N58" s="1" t="s">
         <v>29</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q58" s="4">
         <v>46136</v>
@@ -5566,24 +5570,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>46128</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G59" s="2">
         <v>274.75</v>
@@ -5595,16 +5599,16 @@
         <v>0.5</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q59" s="4">
         <v>46113</v>
@@ -5622,24 +5626,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>46129</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G60" s="2">
         <v>2500</v>
@@ -5651,13 +5655,13 @@
         <v>0.3</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q60" s="4">
         <v>46129</v>
@@ -5675,24 +5679,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>46129</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G61" s="2">
         <v>806.79</v>
@@ -5704,16 +5708,16 @@
         <v>0.25</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q61" s="4">
         <v>46132</v>
@@ -5731,24 +5735,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>46132</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G62" s="2">
         <v>139.44</v>
@@ -5760,16 +5764,16 @@
         <v>0.5</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q62" s="4">
         <v>46160</v>
@@ -5787,24 +5791,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>46134</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G63" s="2">
         <v>987.04</v>
@@ -5816,16 +5820,16 @@
         <v>0.5</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q63" s="4">
         <v>46143</v>
@@ -5843,24 +5847,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>46135</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G64" s="2">
         <v>500</v>
@@ -5872,10 +5876,10 @@
         <v>0.5</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q64" s="4">
         <v>46143</v>
@@ -5890,27 +5894,27 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>46136</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G65" s="2">
-        <v>521.32000000000005</v>
+        <v>521.32</v>
       </c>
       <c r="H65" s="3">
         <v>5980</v>
@@ -5919,16 +5923,16 @@
         <v>0.5</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q65" s="4">
         <v>46139</v>
@@ -5946,24 +5950,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>46139</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G66" s="2">
         <v>500</v>
@@ -5975,10 +5979,10 @@
         <v>0.5</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q66" s="4">
         <v>46143</v>
@@ -5993,21 +5997,21 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>46140</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>26</v>
@@ -6022,19 +6026,19 @@
         <v>0.5</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q67" s="4">
         <v>46143</v>
@@ -6052,24 +6056,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>46141</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G68" s="2">
         <v>1000</v>
@@ -6081,13 +6085,13 @@
         <v>0.5</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q68" s="4">
         <v>45777</v>
@@ -6102,27 +6106,27 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>46142</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G69" s="2">
-        <v>138.30000000000001</v>
+        <v>138.3</v>
       </c>
       <c r="H69" s="3">
         <v>7150</v>
@@ -6131,22 +6135,22 @@
         <v>0.5</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q69" s="4">
         <v>46185</v>
@@ -6164,24 +6168,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>46149</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G70" s="2">
         <v>104.66</v>
@@ -6193,25 +6197,25 @@
         <v>0.5</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q70" s="4">
         <v>46156</v>
@@ -6229,27 +6233,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>46150</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G71" s="2">
-        <v>2148.5819999999999</v>
+        <v>2148.582</v>
       </c>
       <c r="H71" s="3">
         <v>6350</v>
@@ -6258,22 +6262,22 @@
         <v>0.5</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q71" s="4">
         <v>46153</v>
@@ -6291,45 +6295,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>46157</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G72" s="2">
         <v>1000</v>
       </c>
       <c r="H72" s="3">
-        <v>8230.5400000000009</v>
+        <v>8230.54</v>
       </c>
       <c r="I72" s="2">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q72" s="4">
         <v>46174</v>
@@ -6347,24 +6351,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>46160</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G73" s="2">
         <v>1000</v>
@@ -6376,16 +6380,16 @@
         <v>0.03</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q73" s="4">
         <v>46174</v>
@@ -6403,24 +6407,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>46161</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G74" s="2">
         <v>2500</v>
@@ -6432,19 +6436,19 @@
         <v>0.3</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q74" s="4">
         <v>46167</v>
@@ -6462,24 +6466,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>46162</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G75" s="2">
         <v>1018.974</v>
@@ -6491,16 +6495,16 @@
         <v>0.5</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q75" s="4">
         <v>46174</v>
@@ -6518,24 +6522,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>46163</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G76" s="2">
         <v>700</v>
@@ -6547,13 +6551,13 @@
         <v>0.5</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q76" s="4">
         <v>46174</v>
@@ -6571,27 +6575,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>46164</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G77" s="2">
-        <v>998.03899999999999</v>
+        <v>998.039</v>
       </c>
       <c r="H77" s="3">
         <v>5770</v>
@@ -6600,13 +6604,13 @@
         <v>0.5</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q77" s="4">
         <v>46174</v>
@@ -6624,24 +6628,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>46168</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G78" s="2">
         <v>1000</v>
@@ -6650,19 +6654,19 @@
         <v>8265.61</v>
       </c>
       <c r="I78" s="2">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q78" s="4">
         <v>46174</v>
@@ -6680,27 +6684,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>46169</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G79" s="2">
-        <v>983.10599999999999</v>
+        <v>983.106</v>
       </c>
       <c r="H79" s="3">
         <v>5780</v>
@@ -6709,16 +6713,16 @@
         <v>0.5</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q79" s="4">
         <v>46174</v>
@@ -6736,24 +6740,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>46170</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G80" s="2">
         <v>1000</v>
@@ -6765,16 +6769,16 @@
         <v>0.03</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q80" s="4">
         <v>46204</v>
@@ -6792,24 +6796,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>46171</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G81" s="2">
         <v>1000</v>
@@ -6821,16 +6825,16 @@
         <v>0.03</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q81" s="4">
         <v>46204</v>
@@ -6848,24 +6852,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>46181</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G82" s="2">
         <v>1000</v>
@@ -6877,16 +6881,16 @@
         <v>0.03</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q82" s="4">
         <v>46204</v>
@@ -6904,24 +6908,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>46182</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G83" s="2">
         <v>1000</v>
@@ -6933,16 +6937,16 @@
         <v>0.03</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q83" s="4">
         <v>46204</v>
@@ -6960,24 +6964,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>46185</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G84" s="2">
         <v>960.98</v>
@@ -6989,16 +6993,16 @@
         <v>0.5</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q84" s="4">
         <v>46189</v>
@@ -7016,24 +7020,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>46185</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G85" s="2">
         <v>500</v>
@@ -7045,19 +7049,19 @@
         <v>0.5</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q85" s="4">
         <v>46204</v>
@@ -7075,24 +7079,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>46185</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G86" s="2">
         <v>500</v>
@@ -7104,16 +7108,16 @@
         <v>0.5</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q86" s="4">
         <v>46235</v>
@@ -7131,24 +7135,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>46188</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G87" s="2">
         <v>69.73</v>
@@ -7160,13 +7164,13 @@
         <v>0.5</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q87" s="4">
         <v>46220</v>
@@ -7184,24 +7188,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>46195</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G88" s="2">
         <v>2500</v>
@@ -7213,16 +7217,16 @@
         <v>0.3</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q88" s="4">
         <v>46196</v>
@@ -7240,24 +7244,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>46196</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G89" s="2">
         <v>500</v>
@@ -7269,19 +7273,19 @@
         <v>0.5</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q89" s="4">
         <v>46218</v>
@@ -7299,24 +7303,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>46196</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G90" s="2">
         <v>500</v>
@@ -7328,19 +7332,19 @@
         <v>0.5</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q90" s="4">
         <v>46235</v>
@@ -7358,24 +7362,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>46197</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G91" s="2">
         <v>146.71</v>
@@ -7387,13 +7391,13 @@
         <v>1</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q91" s="4">
         <v>46253</v>
@@ -7411,24 +7415,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>46197</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G92" s="2">
         <v>1000</v>
@@ -7440,16 +7444,16 @@
         <v>0.03</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q92" s="4">
         <v>46235</v>
@@ -7467,24 +7471,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>46204</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G93" s="2">
         <v>1000</v>
@@ -7496,16 +7500,16 @@
         <v>0.03</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q93" s="4">
         <v>46235</v>
@@ -7523,27 +7527,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>46206</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G94" s="2">
-        <v>37.369999999999997</v>
+        <v>37.37</v>
       </c>
       <c r="H94" s="3">
         <v>5600</v>
@@ -7552,13 +7556,13 @@
         <v>0.5</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q94" s="4">
         <v>46211</v>
@@ -7576,24 +7580,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>46209</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G95" s="2">
         <v>70</v>
@@ -7605,16 +7609,16 @@
         <v>1</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q95" s="4">
         <v>46258</v>
@@ -7632,24 +7636,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>46210</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G96" s="2">
         <v>105</v>
@@ -7661,16 +7665,16 @@
         <v>1</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q96" s="4">
         <v>46276</v>
@@ -7688,24 +7692,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>46210</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G97" s="2">
         <v>79.19</v>
@@ -7717,13 +7721,13 @@
         <v>0.5</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q97" s="4">
         <v>46213</v>
@@ -7741,24 +7745,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>46218</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G98" s="2">
         <v>1000</v>
@@ -7770,13 +7774,13 @@
         <v>0.25</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q98" s="4">
         <v>46235</v>
@@ -7794,24 +7798,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>46218</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G99" s="2">
         <v>78.91</v>
@@ -7823,13 +7827,13 @@
         <v>0.5</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q99" s="4">
         <v>46219</v>
@@ -7847,24 +7851,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>46219</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G100" s="2">
         <v>1033.92</v>
@@ -7876,13 +7880,13 @@
         <v>0.25</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q100" s="4">
         <v>46235</v>
@@ -7900,27 +7904,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>46219</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G101" s="2">
-        <v>80.569999999999993</v>
+        <v>80.57</v>
       </c>
       <c r="H101" s="3">
         <v>5770</v>
@@ -7929,13 +7933,13 @@
         <v>0.5</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q101" s="4">
         <v>46226</v>
@@ -7953,24 +7957,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>46220</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G102" s="2">
         <v>1000</v>
@@ -7982,16 +7986,16 @@
         <v>0.03</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q102" s="4">
         <v>46235</v>
@@ -8009,24 +8013,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>46224</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G103" s="2">
         <v>105</v>
@@ -8038,13 +8042,13 @@
         <v>1</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q103" s="4">
         <v>46267</v>
@@ -8059,24 +8063,24 @@
         <v>46306</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>46226</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G104" s="2">
         <v>140</v>
@@ -8088,10 +8092,10 @@
         <v>1</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q104" s="4">
         <v>46280</v>
@@ -8106,24 +8110,24 @@
         <v>46319</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>46226</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G105" s="2">
         <v>1000</v>
@@ -8135,16 +8139,16 @@
         <v>0.03</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P105" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q105" s="4">
         <v>46235</v>
@@ -8162,7 +8166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>46227</v>
       </c>
@@ -8170,7 +8174,7 @@
         <v>22</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>24</v>
@@ -8182,7 +8186,7 @@
         <v>26</v>
       </c>
       <c r="G106" s="2">
-        <v>73.959999999999994</v>
+        <v>73.96</v>
       </c>
       <c r="H106" s="3">
         <v>7050</v>
@@ -8191,13 +8195,13 @@
         <v>1</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q106" s="4">
         <v>46230</v>
@@ -8215,24 +8219,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>46231</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G107" s="2">
         <v>1008.36</v>
@@ -8244,13 +8248,13 @@
         <v>0.5</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Q107" s="4">
         <v>46235</v>
@@ -8268,24 +8272,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>46231</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G108" s="2">
         <v>1000</v>
@@ -8297,16 +8301,16 @@
         <v>0.03</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O108" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P108" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q108" s="4">
         <v>46296</v>
@@ -8321,24 +8325,24 @@
         <v>46338</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>46231</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G109" s="2">
         <v>1000</v>
@@ -8350,16 +8354,16 @@
         <v>0.03</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O109" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P109" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q109" s="4">
         <v>46327</v>
@@ -8374,24 +8378,24 @@
         <v>46367</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>46233</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G110" s="2">
         <v>2500</v>
@@ -8403,16 +8407,16 @@
         <v>0.3</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Q110" s="4">
         <v>46233</v>
@@ -8430,7 +8434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>46234</v>
       </c>
@@ -8438,16 +8442,16 @@
         <v>22</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G111" s="2">
         <v>70</v>
@@ -8459,10 +8463,10 @@
         <v>0.5</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q111" s="4">
         <v>46295</v>
@@ -8477,24 +8481,24 @@
         <v>46331</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>46238</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G112" s="2">
         <v>1000</v>
@@ -8506,10 +8510,10 @@
         <v>0.5</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q112" s="4">
         <v>46266</v>
@@ -8524,24 +8528,24 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>46238</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G113" s="2">
         <v>500</v>
@@ -8553,10 +8557,10 @@
         <v>0.5</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q113" s="4">
         <v>46266</v>
@@ -8571,24 +8575,24 @@
         <v>46338</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>46239</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G114" s="2">
         <v>140</v>
@@ -8600,10 +8604,10 @@
         <v>1</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q114" s="4">
         <v>46300</v>
@@ -8618,24 +8622,24 @@
         <v>46340</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>46239</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G115" s="2">
         <v>1000</v>
@@ -8647,16 +8651,16 @@
         <v>0.03</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O115" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P115" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q115" s="4">
         <v>46266</v>
@@ -8674,7 +8678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>46241</v>
       </c>
@@ -8682,13 +8686,13 @@
         <v>22</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>26</v>
@@ -8703,13 +8707,13 @@
         <v>1</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Q116" s="4">
         <v>46248</v>
@@ -8724,24 +8728,24 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>46241</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G117" s="2">
         <v>200</v>
@@ -8753,16 +8757,16 @@
         <v>1</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q117" s="4">
         <v>46245</v>
@@ -8780,24 +8784,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>46246</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G118" s="2">
         <v>105</v>
@@ -8809,16 +8813,16 @@
         <v>0.5</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O118" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="Q118" s="4">
         <v>46261</v>
@@ -8836,24 +8840,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>46248</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G119" s="2">
         <v>1000</v>
@@ -8865,16 +8869,16 @@
         <v>0.03</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O119" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P119" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q119" s="4">
         <v>46266</v>
@@ -8892,24 +8896,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>46252</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G120" s="2">
         <v>140</v>
@@ -8921,16 +8925,16 @@
         <v>0.5</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O120" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="Q120" s="4">
         <v>46258</v>
@@ -8948,24 +8952,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>46254</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G121" s="2">
         <v>501.95</v>
@@ -8977,16 +8981,16 @@
         <v>0.3</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O121" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q121" s="4">
         <v>46279</v>
@@ -9004,24 +9008,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>46254</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G122" s="2">
         <v>1000</v>
@@ -9033,16 +9037,16 @@
         <v>0.03</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O122" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q122" s="4">
         <v>46266</v>
@@ -9060,24 +9064,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>46259</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G123" s="2">
         <v>140</v>
@@ -9089,10 +9093,10 @@
         <v>0.5</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q123" s="4">
         <v>46309</v>
@@ -9107,24 +9111,24 @@
         <v>46363</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
         <v>46259</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G124" s="2">
         <v>2000</v>
@@ -9136,13 +9140,13 @@
         <v>0.25</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N124" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Q124" s="4">
         <v>46266</v>
@@ -9160,24 +9164,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>46260</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G125" s="2">
         <v>240</v>
@@ -9189,19 +9193,19 @@
         <v>1</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O125" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Q125" s="4">
         <v>46262</v>
@@ -9219,24 +9223,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>46261</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G126" s="2">
         <v>1000</v>
@@ -9248,13 +9252,13 @@
         <v>0.25</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Q126" s="4">
         <v>46265</v>
@@ -9272,7 +9276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>46261</v>
       </c>
@@ -9280,13 +9284,13 @@
         <v>22</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>26</v>
@@ -9301,10 +9305,10 @@
         <v>1</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q127" s="4">
         <v>46266</v>
@@ -9319,7 +9323,7 @@
         <v>46320</v>
       </c>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>46261</v>
       </c>
@@ -9327,13 +9331,13 @@
         <v>22</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>26</v>
@@ -9348,10 +9352,10 @@
         <v>1</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q128" s="4">
         <v>46296</v>
@@ -9366,24 +9370,24 @@
         <v>46352</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>46262</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G129" s="2">
         <v>41.18</v>
@@ -9395,13 +9399,13 @@
         <v>0.5</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N129" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Q129" s="4">
         <v>46265</v>
@@ -9419,24 +9423,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>46262</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G130" s="2">
         <v>1000</v>
@@ -9448,13 +9452,13 @@
         <v>0.25</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N130" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q130" s="4">
         <v>46280</v>
@@ -9472,24 +9476,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>46262</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G131" s="2">
         <v>1000</v>
@@ -9501,13 +9505,13 @@
         <v>0.25</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N131" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Q131" s="4">
         <v>46296</v>
@@ -9522,24 +9526,24 @@
         <v>46325</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>46262</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G132" s="2">
         <v>180</v>
@@ -9551,10 +9555,10 @@
         <v>1</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q132" s="4">
         <v>46265</v>
@@ -9569,24 +9573,24 @@
         <v>46306</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>46265</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G133" s="2">
         <v>2500</v>
@@ -9598,13 +9602,13 @@
         <v>0.3</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q133" s="4">
         <v>46265</v>
@@ -9619,24 +9623,24 @@
         <v>46345</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>46265</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G134" s="2">
         <v>120</v>
@@ -9648,16 +9652,16 @@
         <v>1</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Q134" s="4">
         <v>46266</v>
@@ -9675,24 +9679,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>46267</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G135" s="2">
         <v>1500</v>
@@ -9704,16 +9708,16 @@
         <v>0.3</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Q135" s="4">
         <v>46314</v>
@@ -9731,24 +9735,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>46268</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G136" s="2">
         <v>1000</v>
@@ -9760,13 +9764,13 @@
         <v>0.5</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Q136" s="4">
         <v>46272</v>
@@ -9781,24 +9785,24 @@
         <v>46310</v>
       </c>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>46274</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G137" s="2">
         <v>41.56</v>
@@ -9810,16 +9814,16 @@
         <v>0.5</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Q137" s="4">
         <v>46274</v>
@@ -9837,24 +9841,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
         <v>46275</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G138" s="2">
         <v>1000</v>
@@ -9866,10 +9870,10 @@
         <v>0.3</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="Q138" s="4">
         <v>46328</v>
@@ -9884,24 +9888,24 @@
         <v>46373</v>
       </c>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>46275</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G139" s="2">
         <v>500</v>
@@ -9913,10 +9917,10 @@
         <v>0.5</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q139" s="4">
         <v>46300</v>
@@ -9931,24 +9935,24 @@
         <v>46338</v>
       </c>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
         <v>46276</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G140" s="2">
         <v>500</v>
@@ -9960,16 +9964,16 @@
         <v>0.5</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="Q140" s="4">
         <v>46328</v>
@@ -9984,24 +9988,24 @@
         <v>46367</v>
       </c>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>46279</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G141" s="2">
         <v>1000</v>
@@ -10013,13 +10017,13 @@
         <v>0.3</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Q141" s="4">
         <v>46335</v>
@@ -10034,7 +10038,7 @@
         <v>46369</v>
       </c>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
         <v>46280</v>
       </c>
@@ -10042,16 +10046,16 @@
         <v>22</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G142" s="2">
         <v>105</v>
@@ -10063,10 +10067,10 @@
         <v>0.5</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q142" s="4">
         <v>46314</v>
@@ -10081,7 +10085,7 @@
         <v>46354</v>
       </c>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>46280</v>
       </c>
@@ -10089,16 +10093,16 @@
         <v>22</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G143" s="2">
         <v>105</v>
@@ -10110,10 +10114,10 @@
         <v>0.5</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q143" s="4">
         <v>46349</v>
@@ -10128,24 +10132,24 @@
         <v>46384</v>
       </c>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>46281</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G144" s="2">
         <v>1000</v>
@@ -10157,13 +10161,13 @@
         <v>0.25</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Q144" s="4">
         <v>46296</v>
@@ -10178,24 +10182,24 @@
         <v>46341</v>
       </c>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>46286</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G145" s="2">
         <v>1000</v>
@@ -10207,16 +10211,16 @@
         <v>0.5</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P145" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="Q145" s="4">
         <v>46328</v>
@@ -10231,24 +10235,24 @@
         <v>46367</v>
       </c>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
         <v>46287</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G146" s="2">
         <v>84.82</v>
@@ -10260,13 +10264,13 @@
         <v>0.5</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Q146" s="4">
         <v>46287</v>
@@ -10284,24 +10288,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>46287</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G147" s="2">
         <v>150</v>
@@ -10313,13 +10317,13 @@
         <v>0.5</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N147" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q147" s="4">
         <v>46315</v>
@@ -10334,7 +10338,7 @@
         <v>46352</v>
       </c>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>46288</v>
       </c>
@@ -10342,16 +10346,16 @@
         <v>22</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G148" s="2">
         <v>108</v>
@@ -10363,10 +10367,10 @@
         <v>0.5</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q148" s="4">
         <v>46370</v>
@@ -10381,24 +10385,24 @@
         <v>46401</v>
       </c>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>46289</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G149" s="2">
         <v>500</v>
@@ -10410,16 +10414,16 @@
         <v>0.5</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P149" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="Q149" s="4">
         <v>46327</v>
@@ -10434,24 +10438,24 @@
         <v>46373</v>
       </c>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>46289</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G150" s="2">
         <v>500</v>
@@ -10463,16 +10467,16 @@
         <v>0.5</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P150" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="Q150" s="4">
         <v>46357</v>
@@ -10487,24 +10491,24 @@
         <v>46404</v>
       </c>
     </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>46289</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G151" s="2">
         <v>160</v>
@@ -10516,10 +10520,10 @@
         <v>1</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Q151" s="4">
         <v>46300</v>
@@ -10534,24 +10538,24 @@
         <v>46317</v>
       </c>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>46294</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G152" s="2">
         <v>80</v>
@@ -10563,10 +10567,10 @@
         <v>0.5</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N152" s="1" t="s">
         <v>29</v>
@@ -10584,7 +10588,7 @@
         <v>46320</v>
       </c>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>46295</v>
       </c>
@@ -10592,7 +10596,7 @@
         <v>22</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>24</v>
@@ -10601,7 +10605,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G153" s="2">
         <v>500</v>
@@ -10613,10 +10617,10 @@
         <v>1</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N153" s="1" t="s">
         <v>29</v>
@@ -10634,24 +10638,24 @@
         <v>46345</v>
       </c>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>46296</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G154" s="2">
         <v>2500</v>
@@ -10663,16 +10667,16 @@
         <v>0.3</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="Q154" s="4">
         <v>46300</v>
@@ -10687,24 +10691,24 @@
         <v>46374</v>
       </c>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>46297</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G155" s="2">
         <v>1000</v>
@@ -10716,10 +10720,10 @@
         <v>0.25</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Q155" s="4">
         <v>46328</v>
@@ -10734,24 +10738,24 @@
         <v>46371</v>
       </c>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>46302</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G156" s="2">
         <v>350</v>
@@ -10763,10 +10767,10 @@
         <v>0.5</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N156" s="1" t="s">
         <v>29</v>
@@ -10784,7 +10788,7 @@
         <v>46367</v>
       </c>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>46302</v>
       </c>
@@ -10792,16 +10796,16 @@
         <v>22</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G157" s="2">
         <v>500</v>
@@ -10813,10 +10817,10 @@
         <v>0.5</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Q157" s="4">
         <v>46303</v>
@@ -10831,24 +10835,24 @@
         <v>46341</v>
       </c>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>46302</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="D158" s="5">
+        <v>634</v>
+      </c>
+      <c r="D158" s="6">
         <v>26</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G158" s="2">
         <v>80</v>
@@ -10860,10 +10864,10 @@
         <v>0.5</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N158" s="1" t="s">
         <v>29</v>
@@ -10881,162 +10885,162 @@
         <v>46324</v>
       </c>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="I160" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="J160" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N160" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="Q160" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R160" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S160" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="T160" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="U160" s="1" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="161" spans="3:21" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="161" spans="10:14" x14ac:dyDescent="0.25">
       <c r="J161" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="162" spans="3:21" x14ac:dyDescent="0.3">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="162" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J162" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="163" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="D163" s="6"/>
-    </row>
-    <row r="165" spans="3:21" x14ac:dyDescent="0.3">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="163" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D163" s="7"/>
+    </row>
+    <row r="165" spans="13:20" x14ac:dyDescent="0.25">
       <c r="M165" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="P165" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="T165" s="4"/>
     </row>
-    <row r="166" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I166" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="P166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="Q166" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="R166" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="S166" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="T166" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="U166" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>